--- a/artfynd/A 44491-2024 artfynd.xlsx
+++ b/artfynd/A 44491-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120417527</v>
+        <v>120415964</v>
       </c>
       <c r="B2" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581404</v>
+        <v>581429</v>
       </c>
       <c r="R2" t="n">
-        <v>7056801</v>
+        <v>7056767</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120414867</v>
+        <v>120413982</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581463</v>
+        <v>581605</v>
       </c>
       <c r="R3" t="n">
-        <v>7056818</v>
+        <v>7056913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120414134</v>
+        <v>120415855</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +920,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581571</v>
+        <v>581426</v>
       </c>
       <c r="R4" t="n">
-        <v>7056908</v>
+        <v>7056764</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120413881</v>
+        <v>120415685</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,30 +1041,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1059,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581588</v>
+        <v>581446</v>
       </c>
       <c r="R5" t="n">
-        <v>7056845</v>
+        <v>7056767</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120414296</v>
+        <v>120413881</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,38 +1158,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581515</v>
+        <v>581588</v>
       </c>
       <c r="R6" t="n">
-        <v>7056856</v>
+        <v>7056845</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,12 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,22 +1250,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120417963</v>
+        <v>120413128</v>
       </c>
       <c r="B7" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,21 +1278,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581536</v>
+        <v>581627</v>
       </c>
       <c r="R7" t="n">
-        <v>7056710</v>
+        <v>7056700</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1477,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120413663</v>
+        <v>120415894</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>5169</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,38 +1503,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581594</v>
+        <v>581399</v>
       </c>
       <c r="R9" t="n">
-        <v>7056775</v>
+        <v>7056765</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1581,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,22 +1596,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120414673</v>
+        <v>120415813</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,42 +1620,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581456</v>
+        <v>581427</v>
       </c>
       <c r="R10" t="n">
-        <v>7056835</v>
+        <v>7056778</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1693,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,22 +1708,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120415732</v>
+        <v>120414673</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,38 +1732,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581439</v>
+        <v>581456</v>
       </c>
       <c r="R11" t="n">
-        <v>7056768</v>
+        <v>7056835</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,11 +1812,6 @@
           <t>11:04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1810,19 +1824,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120414554</v>
+        <v>120415839</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1862,10 +1876,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581467</v>
+        <v>581411</v>
       </c>
       <c r="R12" t="n">
-        <v>7056835</v>
+        <v>7056774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1911,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,12 +1921,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120417941</v>
+        <v>120417527</v>
       </c>
       <c r="B13" t="n">
-        <v>78279</v>
+        <v>82321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,21 +1969,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1979,10 +1993,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581521</v>
+        <v>581404</v>
       </c>
       <c r="R13" t="n">
-        <v>7056713</v>
+        <v>7056801</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2028,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2038,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120417611</v>
+        <v>120417662</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,21 +2081,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2091,10 +2105,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581420</v>
+        <v>581434</v>
       </c>
       <c r="R14" t="n">
-        <v>7056797</v>
+        <v>7056811</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2140,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2150,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,22 +2165,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120416085</v>
+        <v>120417814</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>56535</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,20 +2189,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2197,19 +2211,29 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581400</v>
+        <v>581488</v>
       </c>
       <c r="R15" t="n">
-        <v>7056768</v>
+        <v>7056733</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2238,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,12 +2272,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,22 +2287,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120417685</v>
+        <v>120417963</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,21 +2315,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2320,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581428</v>
+        <v>581536</v>
       </c>
       <c r="R16" t="n">
-        <v>7056812</v>
+        <v>7056710</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,7 +2411,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120415964</v>
+        <v>120417731</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2427,12 +2446,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2441,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581429</v>
+        <v>581441</v>
       </c>
       <c r="R17" t="n">
-        <v>7056767</v>
+        <v>7056809</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,22 +2520,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120417911</v>
+        <v>120417462</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>95225</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,21 +2548,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2553,10 +2572,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581484</v>
+        <v>581378</v>
       </c>
       <c r="R18" t="n">
-        <v>7056713</v>
+        <v>7056810</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,22 +2632,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120413378</v>
+        <v>120416085</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2637,42 +2656,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581626</v>
+        <v>581400</v>
       </c>
       <c r="R19" t="n">
-        <v>7056697</v>
+        <v>7056768</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2704,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2714,7 +2729,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120413917</v>
+        <v>120413663</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2753,42 +2773,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581610</v>
+        <v>581594</v>
       </c>
       <c r="R20" t="n">
-        <v>7056879</v>
+        <v>7056775</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2820,7 +2836,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,7 +2846,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,19 +2861,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120415835</v>
+        <v>120416014</v>
       </c>
       <c r="B21" t="n">
         <v>79623</v>
@@ -2897,10 +2913,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581425</v>
+        <v>581399</v>
       </c>
       <c r="R21" t="n">
-        <v>7056761</v>
+        <v>7056764</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2932,7 +2948,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2942,7 +2958,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,22 +2973,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120415855</v>
+        <v>120415835</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,43 +3001,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581426</v>
+        <v>581425</v>
       </c>
       <c r="R22" t="n">
-        <v>7056764</v>
+        <v>7056761</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,7 +3060,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3063,7 +3070,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3097,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120413441</v>
+        <v>120413917</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,38 +3109,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581631</v>
+        <v>581610</v>
       </c>
       <c r="R23" t="n">
-        <v>7056710</v>
+        <v>7056879</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3176,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3175,7 +3186,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3202,10 +3213,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120413128</v>
+        <v>120414554</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3218,21 +3229,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3242,10 +3253,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581627</v>
+        <v>581467</v>
       </c>
       <c r="R24" t="n">
-        <v>7056700</v>
+        <v>7056835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3277,7 +3288,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3287,7 +3298,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3314,10 +3330,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120415839</v>
+        <v>120415820</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3330,21 +3346,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3354,10 +3370,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581411</v>
+        <v>581434</v>
       </c>
       <c r="R25" t="n">
-        <v>7056774</v>
+        <v>7056778</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3389,7 +3405,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3399,12 +3415,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,10 +3442,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120415894</v>
+        <v>120417941</v>
       </c>
       <c r="B26" t="n">
-        <v>5169</v>
+        <v>78279</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3443,43 +3454,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581399</v>
+        <v>581521</v>
       </c>
       <c r="R26" t="n">
-        <v>7056765</v>
+        <v>7056713</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3511,7 +3517,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3521,7 +3527,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3548,10 +3554,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120417497</v>
+        <v>120415832</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3564,34 +3570,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581473</v>
+        <v>581418</v>
       </c>
       <c r="R27" t="n">
-        <v>7056827</v>
+        <v>7056773</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3623,7 +3634,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3633,7 +3644,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3648,22 +3659,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120414432</v>
+        <v>120415732</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3676,21 +3687,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3700,10 +3711,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581476</v>
+        <v>581439</v>
       </c>
       <c r="R28" t="n">
-        <v>7056858</v>
+        <v>7056768</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3735,7 +3746,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,12 +3756,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lunglav på asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3777,10 +3788,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120415304</v>
+        <v>120417685</v>
       </c>
       <c r="B29" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3793,21 +3804,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3817,10 +3828,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581476</v>
+        <v>581428</v>
       </c>
       <c r="R29" t="n">
-        <v>7056796</v>
+        <v>7056812</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3852,7 +3863,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3862,7 +3873,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,22 +3888,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120413439</v>
+        <v>120417801</v>
       </c>
       <c r="B30" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3901,25 +3912,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3929,10 +3940,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581650</v>
+        <v>581511</v>
       </c>
       <c r="R30" t="n">
-        <v>7056730</v>
+        <v>7056763</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3964,7 +3975,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3974,7 +3985,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3989,22 +4005,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120415685</v>
+        <v>120414296</v>
       </c>
       <c r="B31" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4017,16 +4033,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4035,21 +4051,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581446</v>
+        <v>581515</v>
       </c>
       <c r="R31" t="n">
-        <v>7056767</v>
+        <v>7056856</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4081,7 +4092,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4091,7 +4102,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4106,22 +4122,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120413560</v>
+        <v>120415304</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4134,21 +4150,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4158,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581627</v>
+        <v>581476</v>
       </c>
       <c r="R32" t="n">
-        <v>7056772</v>
+        <v>7056796</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4193,7 +4209,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4203,7 +4219,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4218,22 +4234,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120413690</v>
+        <v>120414445</v>
       </c>
       <c r="B33" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4242,20 +4258,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4263,14 +4279,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4279,10 +4291,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581626</v>
+        <v>581491</v>
       </c>
       <c r="R33" t="n">
-        <v>7056776</v>
+        <v>7056878</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4314,7 +4326,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4324,7 +4336,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4351,10 +4363,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120413982</v>
+        <v>120414134</v>
       </c>
       <c r="B34" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4363,38 +4375,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581605</v>
+        <v>581571</v>
       </c>
       <c r="R34" t="n">
-        <v>7056913</v>
+        <v>7056908</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4426,7 +4442,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4436,7 +4452,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4451,22 +4467,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120413757</v>
+        <v>120414233</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4475,25 +4491,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4503,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581599</v>
+        <v>581514</v>
       </c>
       <c r="R35" t="n">
-        <v>7056800</v>
+        <v>7056850</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4538,7 +4554,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4548,7 +4564,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4575,10 +4596,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120415820</v>
+        <v>120413912</v>
       </c>
       <c r="B36" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4591,21 +4612,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4615,10 +4636,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581434</v>
+        <v>581608</v>
       </c>
       <c r="R36" t="n">
-        <v>7056778</v>
+        <v>7056867</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4650,7 +4671,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4660,7 +4681,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4675,22 +4696,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120415813</v>
+        <v>120417611</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4703,21 +4724,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4727,10 +4748,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581427</v>
+        <v>581420</v>
       </c>
       <c r="R37" t="n">
-        <v>7056778</v>
+        <v>7056797</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4762,7 +4783,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4772,7 +4793,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4799,10 +4820,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120418034</v>
+        <v>120413378</v>
       </c>
       <c r="B38" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4811,38 +4832,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581578</v>
+        <v>581626</v>
       </c>
       <c r="R38" t="n">
-        <v>7056727</v>
+        <v>7056697</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4874,7 +4899,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4884,7 +4909,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4911,10 +4936,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120415832</v>
+        <v>120413439</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4923,43 +4948,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581418</v>
+        <v>581650</v>
       </c>
       <c r="R39" t="n">
-        <v>7056773</v>
+        <v>7056730</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4991,7 +5011,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5001,7 +5021,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5028,10 +5048,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120417462</v>
+        <v>120414428</v>
       </c>
       <c r="B40" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5040,25 +5060,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5068,10 +5088,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581378</v>
+        <v>581533</v>
       </c>
       <c r="R40" t="n">
-        <v>7056810</v>
+        <v>7056856</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5103,7 +5123,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5113,7 +5133,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5128,19 +5148,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120417662</v>
+        <v>120413560</v>
       </c>
       <c r="B41" t="n">
         <v>78542</v>
@@ -5180,10 +5200,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581434</v>
+        <v>581627</v>
       </c>
       <c r="R41" t="n">
-        <v>7056811</v>
+        <v>7056772</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5215,7 +5235,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5225,7 +5245,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5240,22 +5260,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120417814</v>
+        <v>120417497</v>
       </c>
       <c r="B42" t="n">
-        <v>56535</v>
+        <v>79623</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5264,51 +5284,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102613</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581488</v>
+        <v>581473</v>
       </c>
       <c r="R42" t="n">
-        <v>7056733</v>
+        <v>7056827</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5337,7 +5347,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5347,7 +5357,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5362,12 +5372,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5486,7 +5496,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120414233</v>
+        <v>120414432</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5526,10 +5536,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581514</v>
+        <v>581476</v>
       </c>
       <c r="R44" t="n">
-        <v>7056850</v>
+        <v>7056858</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5561,7 +5571,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5571,7 +5581,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5603,10 +5613,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120417801</v>
+        <v>120414155</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5619,34 +5629,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581511</v>
+        <v>581536</v>
       </c>
       <c r="R45" t="n">
-        <v>7056763</v>
+        <v>7056900</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5678,7 +5688,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5688,12 +5698,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5720,10 +5725,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120413734</v>
+        <v>120413757</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5732,43 +5737,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581614</v>
+        <v>581599</v>
       </c>
       <c r="R46" t="n">
-        <v>7056765</v>
+        <v>7056800</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5825,22 +5825,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120413912</v>
+        <v>120413441</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5853,21 +5853,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581608</v>
+        <v>581631</v>
       </c>
       <c r="R47" t="n">
-        <v>7056867</v>
+        <v>7056710</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5949,10 +5949,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120413604</v>
+        <v>120413734</v>
       </c>
       <c r="B48" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5965,34 +5965,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581637</v>
+        <v>581614</v>
       </c>
       <c r="R48" t="n">
-        <v>7056775</v>
+        <v>7056765</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6024,7 +6029,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6034,7 +6039,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6049,12 +6054,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6173,10 +6178,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120414540</v>
+        <v>120418063</v>
       </c>
       <c r="B50" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6185,25 +6190,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6213,10 +6218,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581464</v>
+        <v>581559</v>
       </c>
       <c r="R50" t="n">
-        <v>7056839</v>
+        <v>7056729</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6248,7 +6253,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6258,7 +6263,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6273,22 +6278,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120414428</v>
+        <v>120417911</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6297,25 +6302,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6325,10 +6330,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581533</v>
+        <v>581484</v>
       </c>
       <c r="R51" t="n">
-        <v>7056856</v>
+        <v>7056713</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6360,7 +6365,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6370,7 +6375,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6397,10 +6402,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120418063</v>
+        <v>120417594</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6409,38 +6414,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581559</v>
+        <v>581404</v>
       </c>
       <c r="R52" t="n">
-        <v>7056729</v>
+        <v>7056792</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6472,7 +6481,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6482,7 +6491,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6509,7 +6518,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120416014</v>
+        <v>120413604</v>
       </c>
       <c r="B53" t="n">
         <v>79623</v>
@@ -6549,10 +6558,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581399</v>
+        <v>581637</v>
       </c>
       <c r="R53" t="n">
-        <v>7056764</v>
+        <v>7056775</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6584,7 +6593,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6594,7 +6603,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6621,10 +6630,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120413054</v>
+        <v>120414867</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6637,21 +6646,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6661,10 +6670,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581595</v>
+        <v>581463</v>
       </c>
       <c r="R54" t="n">
-        <v>7056742</v>
+        <v>7056818</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6696,7 +6705,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6706,12 +6715,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6726,22 +6730,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120414155</v>
+        <v>120418034</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6754,34 +6758,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581536</v>
+        <v>581578</v>
       </c>
       <c r="R55" t="n">
-        <v>7056900</v>
+        <v>7056727</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6813,7 +6817,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6823,7 +6827,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6850,7 +6854,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120414445</v>
+        <v>120413054</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6884,21 +6888,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581491</v>
+        <v>581595</v>
       </c>
       <c r="R56" t="n">
-        <v>7056878</v>
+        <v>7056742</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6930,7 +6929,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6940,7 +6939,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6955,22 +6959,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120417594</v>
+        <v>120413690</v>
       </c>
       <c r="B57" t="n">
-        <v>97930</v>
+        <v>57431</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6979,30 +6983,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7011,10 +7020,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581404</v>
+        <v>581626</v>
       </c>
       <c r="R57" t="n">
-        <v>7056792</v>
+        <v>7056776</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7046,7 +7055,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7056,7 +7065,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7083,10 +7092,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120417731</v>
+        <v>120414540</v>
       </c>
       <c r="B58" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7095,47 +7104,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581441</v>
+        <v>581464</v>
       </c>
       <c r="R58" t="n">
-        <v>7056809</v>
+        <v>7056839</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7192,12 +7192,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 44491-2024 artfynd.xlsx
+++ b/artfynd/A 44491-2024 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120415839</v>
+        <v>120417527</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581411</v>
+        <v>581404</v>
       </c>
       <c r="R12" t="n">
-        <v>7056774</v>
+        <v>7056801</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1921,12 +1921,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,22 +1936,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120417527</v>
+        <v>120417662</v>
       </c>
       <c r="B13" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,21 +1964,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,10 +1988,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581404</v>
+        <v>581434</v>
       </c>
       <c r="R13" t="n">
-        <v>7056801</v>
+        <v>7056811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,7 +2023,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2038,7 +2033,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120417662</v>
+        <v>120415839</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,21 +2076,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581434</v>
+        <v>581411</v>
       </c>
       <c r="R14" t="n">
-        <v>7056811</v>
+        <v>7056774</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2150,7 +2145,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,12 +2165,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120414233</v>
+        <v>120417611</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4495,21 +4495,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581514</v>
+        <v>581420</v>
       </c>
       <c r="R35" t="n">
-        <v>7056850</v>
+        <v>7056797</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4564,12 +4564,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4596,10 +4591,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120413912</v>
+        <v>120413378</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4608,38 +4603,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581608</v>
+        <v>581626</v>
       </c>
       <c r="R36" t="n">
-        <v>7056867</v>
+        <v>7056697</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4671,7 +4670,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4681,7 +4680,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4708,10 +4707,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120417611</v>
+        <v>120413439</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4720,25 +4719,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4748,10 +4747,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581420</v>
+        <v>581650</v>
       </c>
       <c r="R37" t="n">
-        <v>7056797</v>
+        <v>7056730</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4783,7 +4782,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4793,7 +4792,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4820,10 +4819,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120413378</v>
+        <v>120414233</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4832,42 +4831,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581626</v>
+        <v>581514</v>
       </c>
       <c r="R38" t="n">
-        <v>7056697</v>
+        <v>7056850</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4899,7 +4894,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4909,7 +4904,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4924,22 +4924,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413439</v>
+        <v>120413912</v>
       </c>
       <c r="B39" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4948,25 +4948,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4976,10 +4976,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581650</v>
+        <v>581608</v>
       </c>
       <c r="R39" t="n">
-        <v>7056730</v>
+        <v>7056867</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5036,12 +5036,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 44491-2024 artfynd.xlsx
+++ b/artfynd/A 44491-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120415964</v>
+        <v>120413982</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581429</v>
+        <v>581605</v>
       </c>
       <c r="R2" t="n">
-        <v>7056767</v>
+        <v>7056913</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120413982</v>
+        <v>120414155</v>
       </c>
       <c r="B3" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581605</v>
+        <v>581536</v>
       </c>
       <c r="R3" t="n">
-        <v>7056913</v>
+        <v>7056900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120415855</v>
+        <v>120415832</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,31 +915,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -957,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581426</v>
+        <v>581418</v>
       </c>
       <c r="R4" t="n">
-        <v>7056764</v>
+        <v>7056773</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120415685</v>
+        <v>120413812</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581446</v>
+        <v>581544</v>
       </c>
       <c r="R5" t="n">
-        <v>7056767</v>
+        <v>7056816</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120413881</v>
+        <v>120414432</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,42 +1140,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581588</v>
+        <v>581476</v>
       </c>
       <c r="R6" t="n">
-        <v>7056845</v>
+        <v>7056858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120413128</v>
+        <v>120417941</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581627</v>
+        <v>581521</v>
       </c>
       <c r="R7" t="n">
-        <v>7056700</v>
+        <v>7056713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,22 +1345,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120417640</v>
+        <v>120413757</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581428</v>
+        <v>581599</v>
       </c>
       <c r="R8" t="n">
-        <v>7056812</v>
+        <v>7056800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,12 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120415894</v>
+        <v>120417611</v>
       </c>
       <c r="B9" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,43 +1481,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581399</v>
+        <v>581420</v>
       </c>
       <c r="R9" t="n">
-        <v>7056765</v>
+        <v>7056797</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120415813</v>
+        <v>120414673</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,38 +1593,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581427</v>
+        <v>581456</v>
       </c>
       <c r="R10" t="n">
-        <v>7056778</v>
+        <v>7056835</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,22 +1685,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120414673</v>
+        <v>120417640</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,42 +1709,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581456</v>
+        <v>581428</v>
       </c>
       <c r="R11" t="n">
-        <v>7056835</v>
+        <v>7056812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,7 +1782,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,22 +1802,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120417527</v>
+        <v>120415964</v>
       </c>
       <c r="B12" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,38 +1826,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581404</v>
+        <v>581429</v>
       </c>
       <c r="R12" t="n">
-        <v>7056801</v>
+        <v>7056767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1921,7 +1908,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,22 +1923,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120417662</v>
+        <v>120417527</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,21 +1951,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1988,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581434</v>
+        <v>581404</v>
       </c>
       <c r="R13" t="n">
-        <v>7056811</v>
+        <v>7056801</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2033,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2060,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120415839</v>
+        <v>120413871</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,21 +2063,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2100,10 +2087,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581411</v>
+        <v>581557</v>
       </c>
       <c r="R14" t="n">
-        <v>7056774</v>
+        <v>7056865</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2122,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,12 +2132,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120417814</v>
+        <v>120418063</v>
       </c>
       <c r="B15" t="n">
-        <v>56535</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2189,51 +2171,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581488</v>
+        <v>581559</v>
       </c>
       <c r="R15" t="n">
-        <v>7056733</v>
+        <v>7056729</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2262,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,22 +2259,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120417963</v>
+        <v>120417662</v>
       </c>
       <c r="B16" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2315,21 +2287,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2339,10 +2311,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581536</v>
+        <v>581434</v>
       </c>
       <c r="R16" t="n">
-        <v>7056710</v>
+        <v>7056811</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2356,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,22 +2371,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120417731</v>
+        <v>120415894</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,35 +2395,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2460,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581441</v>
+        <v>581399</v>
       </c>
       <c r="R17" t="n">
-        <v>7056809</v>
+        <v>7056765</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120417462</v>
+        <v>120415732</v>
       </c>
       <c r="B18" t="n">
-        <v>95225</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,25 +2512,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2572,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581378</v>
+        <v>581439</v>
       </c>
       <c r="R18" t="n">
-        <v>7056810</v>
+        <v>7056768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2607,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2585,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Lunglav på asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2644,10 +2617,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120416085</v>
+        <v>120413128</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,21 +2633,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2684,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581400</v>
+        <v>581627</v>
       </c>
       <c r="R19" t="n">
-        <v>7056768</v>
+        <v>7056700</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2719,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,12 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,22 +2717,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120413663</v>
+        <v>120414428</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2777,21 +2745,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2769,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581594</v>
+        <v>581533</v>
       </c>
       <c r="R20" t="n">
-        <v>7056775</v>
+        <v>7056856</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,7 +2804,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2846,7 +2814,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,22 +2829,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120416014</v>
+        <v>120414867</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,21 +2857,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2913,10 +2881,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581399</v>
+        <v>581463</v>
       </c>
       <c r="R21" t="n">
-        <v>7056764</v>
+        <v>7056818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,7 +2916,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,7 +2926,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,22 +2941,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120415835</v>
+        <v>120414296</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,21 +2969,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3025,10 +2993,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581425</v>
+        <v>581515</v>
       </c>
       <c r="R22" t="n">
-        <v>7056761</v>
+        <v>7056856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3060,7 +3028,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3070,7 +3038,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,19 +3058,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120413917</v>
+        <v>120413378</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3141,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581610</v>
+        <v>581626</v>
       </c>
       <c r="R23" t="n">
-        <v>7056879</v>
+        <v>7056697</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3176,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3186,7 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120414554</v>
+        <v>120417462</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>95225</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3225,25 +3198,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3253,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581467</v>
+        <v>581378</v>
       </c>
       <c r="R24" t="n">
-        <v>7056835</v>
+        <v>7056810</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3288,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3298,12 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,7 +3298,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120415820</v>
+        <v>120417685</v>
       </c>
       <c r="B25" t="n">
         <v>79623</v>
@@ -3370,10 +3338,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581434</v>
+        <v>581428</v>
       </c>
       <c r="R25" t="n">
-        <v>7056778</v>
+        <v>7056812</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3405,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3415,7 +3383,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3442,10 +3410,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120417941</v>
+        <v>120417497</v>
       </c>
       <c r="B26" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3458,21 +3426,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3482,10 +3450,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581521</v>
+        <v>581473</v>
       </c>
       <c r="R26" t="n">
-        <v>7056713</v>
+        <v>7056827</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,7 +3485,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3527,7 +3495,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,7 +3522,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120415832</v>
+        <v>120414445</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3599,10 +3567,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581418</v>
+        <v>581491</v>
       </c>
       <c r="R27" t="n">
-        <v>7056773</v>
+        <v>7056878</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3634,7 +3602,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3644,7 +3612,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3659,22 +3627,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120415732</v>
+        <v>120417814</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>56535</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3683,41 +3651,51 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>102613</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581439</v>
+        <v>581488</v>
       </c>
       <c r="R28" t="n">
-        <v>7056768</v>
+        <v>7056733</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3746,7 +3724,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3756,12 +3734,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3788,7 +3761,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120417685</v>
+        <v>120415813</v>
       </c>
       <c r="B29" t="n">
         <v>79623</v>
@@ -3828,10 +3801,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581428</v>
+        <v>581427</v>
       </c>
       <c r="R29" t="n">
-        <v>7056812</v>
+        <v>7056778</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3863,7 +3836,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3873,7 +3846,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3900,10 +3873,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120417801</v>
+        <v>120415855</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3916,34 +3889,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581511</v>
+        <v>581426</v>
       </c>
       <c r="R30" t="n">
-        <v>7056763</v>
+        <v>7056764</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3975,7 +3957,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3985,12 +3967,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4017,10 +3994,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120414296</v>
+        <v>120413663</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4033,21 +4010,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4057,10 +4034,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581515</v>
+        <v>581594</v>
       </c>
       <c r="R31" t="n">
-        <v>7056856</v>
+        <v>7056775</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4092,7 +4069,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4102,12 +4079,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4134,10 +4106,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120415304</v>
+        <v>120413881</v>
       </c>
       <c r="B32" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4146,38 +4118,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581476</v>
+        <v>581588</v>
       </c>
       <c r="R32" t="n">
-        <v>7056796</v>
+        <v>7056845</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4209,7 +4185,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4219,7 +4195,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4246,10 +4222,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120414445</v>
+        <v>120413560</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4262,39 +4238,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581491</v>
+        <v>581627</v>
       </c>
       <c r="R33" t="n">
-        <v>7056878</v>
+        <v>7056772</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4326,7 +4297,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4336,7 +4307,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4351,22 +4322,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120414134</v>
+        <v>120414540</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4375,42 +4346,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581571</v>
+        <v>581464</v>
       </c>
       <c r="R34" t="n">
-        <v>7056908</v>
+        <v>7056839</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4442,7 +4409,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4452,7 +4419,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4467,22 +4434,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120417611</v>
+        <v>120415835</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4495,21 +4462,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4519,10 +4486,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581420</v>
+        <v>581425</v>
       </c>
       <c r="R35" t="n">
-        <v>7056797</v>
+        <v>7056761</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4554,7 +4521,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4564,7 +4531,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,22 +4546,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120413378</v>
+        <v>120413054</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4603,42 +4570,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581626</v>
+        <v>581595</v>
       </c>
       <c r="R36" t="n">
-        <v>7056697</v>
+        <v>7056742</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4670,7 +4633,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4680,7 +4643,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4695,22 +4663,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120413439</v>
+        <v>120413441</v>
       </c>
       <c r="B37" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4719,25 +4687,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4747,10 +4715,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581650</v>
+        <v>581631</v>
       </c>
       <c r="R37" t="n">
-        <v>7056730</v>
+        <v>7056710</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4782,7 +4750,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4792,7 +4760,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4807,22 +4775,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120414233</v>
+        <v>120413604</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4835,21 +4803,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4859,10 +4827,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581514</v>
+        <v>581637</v>
       </c>
       <c r="R38" t="n">
-        <v>7056850</v>
+        <v>7056775</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4894,7 +4862,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4904,12 +4872,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4936,10 +4899,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413912</v>
+        <v>120415820</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4952,21 +4915,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4976,10 +4939,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581608</v>
+        <v>581434</v>
       </c>
       <c r="R39" t="n">
-        <v>7056867</v>
+        <v>7056778</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5011,7 +4974,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5021,7 +4984,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5036,22 +4999,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120414428</v>
+        <v>120415685</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5064,34 +5027,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581533</v>
+        <v>581446</v>
       </c>
       <c r="R40" t="n">
-        <v>7056856</v>
+        <v>7056767</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5123,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5133,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5160,10 +5128,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120413560</v>
+        <v>120413439</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5172,25 +5140,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5200,10 +5168,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581627</v>
+        <v>581650</v>
       </c>
       <c r="R41" t="n">
-        <v>7056772</v>
+        <v>7056730</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5235,7 +5203,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5245,7 +5213,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5272,10 +5240,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120417497</v>
+        <v>120414233</v>
       </c>
       <c r="B42" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5288,21 +5256,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5312,10 +5280,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581473</v>
+        <v>581514</v>
       </c>
       <c r="R42" t="n">
-        <v>7056827</v>
+        <v>7056850</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5347,7 +5315,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5357,7 +5325,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5372,22 +5345,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120413812</v>
+        <v>120413917</v>
       </c>
       <c r="B43" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5396,38 +5369,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581544</v>
+        <v>581610</v>
       </c>
       <c r="R43" t="n">
-        <v>7056816</v>
+        <v>7056879</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5459,7 +5436,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5469,7 +5446,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5484,22 +5461,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120414432</v>
+        <v>120417963</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5512,21 +5489,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5536,10 +5513,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581476</v>
+        <v>581536</v>
       </c>
       <c r="R44" t="n">
-        <v>7056858</v>
+        <v>7056710</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5571,7 +5548,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5581,12 +5558,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5613,7 +5585,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120414155</v>
+        <v>120413912</v>
       </c>
       <c r="B45" t="n">
         <v>78542</v>
@@ -5649,14 +5621,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581536</v>
+        <v>581608</v>
       </c>
       <c r="R45" t="n">
-        <v>7056900</v>
+        <v>7056867</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5688,7 +5660,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5698,7 +5670,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5725,7 +5697,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120413757</v>
+        <v>120417911</v>
       </c>
       <c r="B46" t="n">
         <v>91858</v>
@@ -5765,10 +5737,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581599</v>
+        <v>581484</v>
       </c>
       <c r="R46" t="n">
-        <v>7056800</v>
+        <v>7056713</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5800,7 +5772,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5810,7 +5782,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5825,22 +5797,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120413441</v>
+        <v>120418034</v>
       </c>
       <c r="B47" t="n">
-        <v>90580</v>
+        <v>78278</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5853,21 +5825,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5877,10 +5849,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581631</v>
+        <v>581578</v>
       </c>
       <c r="R47" t="n">
-        <v>7056710</v>
+        <v>7056727</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5912,7 +5884,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5922,7 +5894,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5949,7 +5921,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120413734</v>
+        <v>120414554</v>
       </c>
       <c r="B48" t="n">
         <v>57320</v>
@@ -5983,21 +5955,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581614</v>
+        <v>581467</v>
       </c>
       <c r="R48" t="n">
-        <v>7056765</v>
+        <v>7056835</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6029,7 +5996,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6039,7 +6006,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6054,22 +6026,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120413871</v>
+        <v>120413690</v>
       </c>
       <c r="B49" t="n">
-        <v>79623</v>
+        <v>57431</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6078,38 +6050,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581557</v>
+        <v>581626</v>
       </c>
       <c r="R49" t="n">
-        <v>7056865</v>
+        <v>7056776</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6141,7 +6122,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6151,7 +6132,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6166,22 +6147,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120418063</v>
+        <v>120416014</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6194,21 +6175,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6218,10 +6199,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581559</v>
+        <v>581399</v>
       </c>
       <c r="R50" t="n">
-        <v>7056729</v>
+        <v>7056764</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6253,7 +6234,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6263,7 +6244,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6278,22 +6259,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120417911</v>
+        <v>120415304</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6302,25 +6283,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6330,10 +6311,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581484</v>
+        <v>581476</v>
       </c>
       <c r="R51" t="n">
-        <v>7056713</v>
+        <v>7056796</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6365,7 +6346,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6375,7 +6356,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6402,10 +6383,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120417594</v>
+        <v>120413734</v>
       </c>
       <c r="B52" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6414,30 +6395,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6446,10 +6428,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581404</v>
+        <v>581614</v>
       </c>
       <c r="R52" t="n">
-        <v>7056792</v>
+        <v>7056765</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6481,7 +6463,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6491,7 +6473,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6518,10 +6500,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120413604</v>
+        <v>120415839</v>
       </c>
       <c r="B53" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6534,21 +6516,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6558,10 +6540,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581637</v>
+        <v>581411</v>
       </c>
       <c r="R53" t="n">
-        <v>7056775</v>
+        <v>7056774</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6593,7 +6575,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6603,7 +6585,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6630,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120414867</v>
+        <v>120414134</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6642,38 +6629,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581463</v>
+        <v>581571</v>
       </c>
       <c r="R54" t="n">
-        <v>7056818</v>
+        <v>7056908</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6705,7 +6696,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6715,7 +6706,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6742,10 +6733,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120418034</v>
+        <v>120417594</v>
       </c>
       <c r="B55" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6754,38 +6745,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581578</v>
+        <v>581404</v>
       </c>
       <c r="R55" t="n">
-        <v>7056727</v>
+        <v>7056792</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6817,7 +6812,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6827,7 +6822,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6854,7 +6849,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120413054</v>
+        <v>120416085</v>
       </c>
       <c r="B56" t="n">
         <v>57320</v>
@@ -6894,10 +6889,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581595</v>
+        <v>581400</v>
       </c>
       <c r="R56" t="n">
-        <v>7056742</v>
+        <v>7056768</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6929,7 +6924,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6939,12 +6934,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6959,22 +6954,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120413690</v>
+        <v>120417801</v>
       </c>
       <c r="B57" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6983,20 +6978,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7004,26 +6999,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581626</v>
+        <v>581511</v>
       </c>
       <c r="R57" t="n">
-        <v>7056776</v>
+        <v>7056763</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7055,7 +7041,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7065,7 +7051,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7092,10 +7083,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120414540</v>
+        <v>120417731</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7104,38 +7095,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581464</v>
+        <v>581441</v>
       </c>
       <c r="R58" t="n">
-        <v>7056839</v>
+        <v>7056809</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7192,12 +7192,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 44491-2024 artfynd.xlsx
+++ b/artfynd/A 44491-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120413982</v>
+        <v>120417527</v>
       </c>
       <c r="B2" t="n">
-        <v>95225</v>
+        <v>82321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581605</v>
+        <v>581404</v>
       </c>
       <c r="R2" t="n">
-        <v>7056913</v>
+        <v>7056801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120414155</v>
+        <v>120414428</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581536</v>
+        <v>581533</v>
       </c>
       <c r="R3" t="n">
-        <v>7056900</v>
+        <v>7056856</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120415832</v>
+        <v>120413871</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581418</v>
+        <v>581557</v>
       </c>
       <c r="R4" t="n">
-        <v>7056773</v>
+        <v>7056865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120413812</v>
+        <v>120417640</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581544</v>
+        <v>581428</v>
       </c>
       <c r="R5" t="n">
-        <v>7056816</v>
+        <v>7056812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120414432</v>
+        <v>120417594</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,38 +1140,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581476</v>
+        <v>581404</v>
       </c>
       <c r="R6" t="n">
-        <v>7056858</v>
+        <v>7056792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1232,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120417941</v>
+        <v>120413982</v>
       </c>
       <c r="B7" t="n">
-        <v>78279</v>
+        <v>95225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,38 +1256,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581521</v>
+        <v>581605</v>
       </c>
       <c r="R7" t="n">
-        <v>7056713</v>
+        <v>7056913</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1344,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120413757</v>
+        <v>120417963</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1368,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581599</v>
+        <v>581536</v>
       </c>
       <c r="R8" t="n">
-        <v>7056800</v>
+        <v>7056710</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120417611</v>
+        <v>120414673</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,38 +1480,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581420</v>
+        <v>581456</v>
       </c>
       <c r="R9" t="n">
-        <v>7056797</v>
+        <v>7056835</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,22 +1572,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120414673</v>
+        <v>120413560</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,42 +1596,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581456</v>
+        <v>581627</v>
       </c>
       <c r="R10" t="n">
-        <v>7056835</v>
+        <v>7056772</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,22 +1684,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120417640</v>
+        <v>120417611</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581428</v>
+        <v>581420</v>
       </c>
       <c r="R11" t="n">
-        <v>7056812</v>
+        <v>7056797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,12 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,7 +1808,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120415964</v>
+        <v>120413378</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1849,12 +1843,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1863,10 +1852,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581429</v>
+        <v>581626</v>
       </c>
       <c r="R12" t="n">
-        <v>7056767</v>
+        <v>7056697</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,22 +1912,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120417527</v>
+        <v>120415964</v>
       </c>
       <c r="B13" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,38 +1936,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581404</v>
+        <v>581429</v>
       </c>
       <c r="R13" t="n">
-        <v>7056801</v>
+        <v>7056767</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,22 +2033,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120413871</v>
+        <v>120417911</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,25 +2057,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2087,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581557</v>
+        <v>581484</v>
       </c>
       <c r="R14" t="n">
-        <v>7056865</v>
+        <v>7056713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2132,7 +2130,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,22 +2145,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120418063</v>
+        <v>120415832</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,34 +2173,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581559</v>
+        <v>581418</v>
       </c>
       <c r="R15" t="n">
-        <v>7056729</v>
+        <v>7056773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,22 +2262,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120417662</v>
+        <v>120414445</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,34 +2290,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581434</v>
+        <v>581491</v>
       </c>
       <c r="R16" t="n">
-        <v>7056811</v>
+        <v>7056878</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2354,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,7 +2364,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,10 +2391,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120415894</v>
+        <v>120414155</v>
       </c>
       <c r="B17" t="n">
-        <v>5169</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,43 +2403,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581399</v>
+        <v>581536</v>
       </c>
       <c r="R17" t="n">
-        <v>7056765</v>
+        <v>7056900</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,7 +2466,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2476,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2503,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120415732</v>
+        <v>120415304</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,21 +2519,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2540,10 +2543,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581439</v>
+        <v>581476</v>
       </c>
       <c r="R18" t="n">
-        <v>7056768</v>
+        <v>7056796</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2575,7 +2578,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,12 +2588,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2605,22 +2603,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120413128</v>
+        <v>120413054</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,21 +2631,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2657,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581627</v>
+        <v>581595</v>
       </c>
       <c r="R19" t="n">
-        <v>7056700</v>
+        <v>7056742</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,7 +2700,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,10 +2732,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120414428</v>
+        <v>120417685</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2745,21 +2748,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2769,10 +2772,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581533</v>
+        <v>581428</v>
       </c>
       <c r="R20" t="n">
-        <v>7056856</v>
+        <v>7056812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2804,7 +2807,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2814,7 +2817,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,22 +2832,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120414867</v>
+        <v>120417731</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2853,38 +2856,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581463</v>
+        <v>581441</v>
       </c>
       <c r="R21" t="n">
-        <v>7056818</v>
+        <v>7056809</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2916,7 +2928,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2926,7 +2938,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,10 +2965,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120414296</v>
+        <v>120413917</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2965,38 +2977,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581515</v>
+        <v>581610</v>
       </c>
       <c r="R22" t="n">
-        <v>7056856</v>
+        <v>7056879</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3028,7 +3044,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3038,12 +3054,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3058,22 +3069,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120413378</v>
+        <v>120417497</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3082,42 +3093,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581626</v>
+        <v>581473</v>
       </c>
       <c r="R23" t="n">
-        <v>7056697</v>
+        <v>7056827</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,7 +3156,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,7 +3166,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,10 +3193,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120417462</v>
+        <v>120413881</v>
       </c>
       <c r="B24" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,38 +3205,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581378</v>
+        <v>581588</v>
       </c>
       <c r="R24" t="n">
-        <v>7056810</v>
+        <v>7056845</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3261,7 +3272,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3282,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3286,22 +3297,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120417685</v>
+        <v>120418063</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3314,21 +3325,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3338,10 +3349,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581428</v>
+        <v>581559</v>
       </c>
       <c r="R25" t="n">
-        <v>7056812</v>
+        <v>7056729</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3373,7 +3384,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3383,7 +3394,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3398,22 +3409,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120417497</v>
+        <v>120414554</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3426,21 +3437,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3450,10 +3461,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581473</v>
+        <v>581467</v>
       </c>
       <c r="R26" t="n">
-        <v>7056827</v>
+        <v>7056835</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3485,7 +3496,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3495,7 +3506,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,22 +3526,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120414445</v>
+        <v>120413128</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3538,39 +3554,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581491</v>
+        <v>581627</v>
       </c>
       <c r="R27" t="n">
-        <v>7056878</v>
+        <v>7056700</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3602,7 +3613,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3612,7 +3623,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3627,22 +3638,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120417814</v>
+        <v>120417941</v>
       </c>
       <c r="B28" t="n">
-        <v>56535</v>
+        <v>78279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3651,51 +3662,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581488</v>
+        <v>581521</v>
       </c>
       <c r="R28" t="n">
-        <v>7056733</v>
+        <v>7056713</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3724,7 +3725,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3734,7 +3735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,22 +3750,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120415813</v>
+        <v>120414233</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3777,21 +3778,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3801,10 +3802,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581427</v>
+        <v>581514</v>
       </c>
       <c r="R29" t="n">
-        <v>7056778</v>
+        <v>7056850</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3836,7 +3837,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3846,7 +3847,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3873,10 +3879,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120415855</v>
+        <v>120415839</v>
       </c>
       <c r="B30" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3889,43 +3895,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581426</v>
+        <v>581411</v>
       </c>
       <c r="R30" t="n">
-        <v>7056764</v>
+        <v>7056774</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3957,7 +3954,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3967,7 +3964,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3982,19 +3984,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120413663</v>
+        <v>120415813</v>
       </c>
       <c r="B31" t="n">
         <v>79623</v>
@@ -4034,10 +4036,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581594</v>
+        <v>581427</v>
       </c>
       <c r="R31" t="n">
-        <v>7056775</v>
+        <v>7056778</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4069,7 +4071,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4079,7 +4081,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4106,10 +4108,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120413881</v>
+        <v>120414867</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4118,42 +4120,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581588</v>
+        <v>581463</v>
       </c>
       <c r="R32" t="n">
-        <v>7056845</v>
+        <v>7056818</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4185,7 +4183,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4195,7 +4193,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4222,10 +4220,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120413560</v>
+        <v>120417462</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4234,25 +4232,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4262,10 +4260,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581627</v>
+        <v>581378</v>
       </c>
       <c r="R33" t="n">
-        <v>7056772</v>
+        <v>7056810</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4297,7 +4295,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4307,7 +4305,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4334,10 +4332,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120414540</v>
+        <v>120413734</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4346,38 +4344,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581464</v>
+        <v>581614</v>
       </c>
       <c r="R34" t="n">
-        <v>7056839</v>
+        <v>7056765</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4409,7 +4412,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4419,7 +4422,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4434,19 +4437,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120415835</v>
+        <v>120416014</v>
       </c>
       <c r="B35" t="n">
         <v>79623</v>
@@ -4486,10 +4489,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581425</v>
+        <v>581399</v>
       </c>
       <c r="R35" t="n">
-        <v>7056761</v>
+        <v>7056764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4521,7 +4524,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4531,7 +4534,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,22 +4549,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120413054</v>
+        <v>120417662</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4574,21 +4577,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4598,10 +4601,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581595</v>
+        <v>581434</v>
       </c>
       <c r="R36" t="n">
-        <v>7056742</v>
+        <v>7056811</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4633,7 +4636,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4643,12 +4646,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4663,22 +4661,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120413441</v>
+        <v>120413690</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>57431</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4687,38 +4685,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581631</v>
+        <v>581626</v>
       </c>
       <c r="R37" t="n">
-        <v>7056710</v>
+        <v>7056776</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4750,7 +4757,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4760,7 +4767,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4787,10 +4794,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120413604</v>
+        <v>120414296</v>
       </c>
       <c r="B38" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4803,21 +4810,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4827,10 +4834,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581637</v>
+        <v>581515</v>
       </c>
       <c r="R38" t="n">
-        <v>7056775</v>
+        <v>7056856</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4862,7 +4869,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4872,7 +4879,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4899,7 +4911,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120415820</v>
+        <v>120413812</v>
       </c>
       <c r="B39" t="n">
         <v>79623</v>
@@ -4939,10 +4951,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581434</v>
+        <v>581544</v>
       </c>
       <c r="R39" t="n">
-        <v>7056778</v>
+        <v>7056816</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4974,7 +4986,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4984,7 +4996,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5011,10 +5023,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120415685</v>
+        <v>120415820</v>
       </c>
       <c r="B40" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5027,39 +5039,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581446</v>
+        <v>581434</v>
       </c>
       <c r="R40" t="n">
-        <v>7056767</v>
+        <v>7056778</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5091,7 +5098,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5101,7 +5108,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5116,22 +5123,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120413439</v>
+        <v>120415685</v>
       </c>
       <c r="B41" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5140,38 +5147,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581650</v>
+        <v>581446</v>
       </c>
       <c r="R41" t="n">
-        <v>7056730</v>
+        <v>7056767</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5203,7 +5215,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5213,7 +5225,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5228,22 +5240,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120414233</v>
+        <v>120415894</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>5169</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5252,38 +5264,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581514</v>
+        <v>581399</v>
       </c>
       <c r="R42" t="n">
-        <v>7056850</v>
+        <v>7056765</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5315,7 +5332,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5325,12 +5342,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5345,22 +5357,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120413917</v>
+        <v>120417814</v>
       </c>
       <c r="B43" t="n">
-        <v>97930</v>
+        <v>56535</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5369,30 +5381,36 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5401,13 +5419,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581610</v>
+        <v>581488</v>
       </c>
       <c r="R43" t="n">
-        <v>7056879</v>
+        <v>7056733</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5436,7 +5454,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5446,7 +5464,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5461,22 +5479,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120417963</v>
+        <v>120413439</v>
       </c>
       <c r="B44" t="n">
-        <v>78279</v>
+        <v>90545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5485,25 +5503,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5513,10 +5531,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581536</v>
+        <v>581650</v>
       </c>
       <c r="R44" t="n">
-        <v>7056710</v>
+        <v>7056730</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5548,7 +5566,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5558,7 +5576,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5585,10 +5603,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120413912</v>
+        <v>120415855</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5601,34 +5619,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581608</v>
+        <v>581426</v>
       </c>
       <c r="R45" t="n">
-        <v>7056867</v>
+        <v>7056764</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5660,7 +5687,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5670,7 +5697,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5697,10 +5724,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120417911</v>
+        <v>120414134</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5709,38 +5736,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581484</v>
+        <v>581571</v>
       </c>
       <c r="R46" t="n">
-        <v>7056713</v>
+        <v>7056908</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5772,7 +5803,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5782,7 +5813,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5809,10 +5840,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120418034</v>
+        <v>120413663</v>
       </c>
       <c r="B47" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5825,21 +5856,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5849,10 +5880,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581578</v>
+        <v>581594</v>
       </c>
       <c r="R47" t="n">
-        <v>7056727</v>
+        <v>7056775</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5884,7 +5915,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5894,7 +5925,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5909,22 +5940,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120414554</v>
+        <v>120415732</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5937,21 +5968,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5961,10 +5992,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581467</v>
+        <v>581439</v>
       </c>
       <c r="R48" t="n">
-        <v>7056835</v>
+        <v>7056768</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5996,7 +6027,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6006,12 +6037,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lunglav på asp</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6038,10 +6069,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120413690</v>
+        <v>120413441</v>
       </c>
       <c r="B49" t="n">
-        <v>57431</v>
+        <v>90580</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6050,47 +6081,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581626</v>
+        <v>581631</v>
       </c>
       <c r="R49" t="n">
-        <v>7056776</v>
+        <v>7056710</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6122,7 +6144,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6132,7 +6154,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6159,10 +6181,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120416014</v>
+        <v>120417801</v>
       </c>
       <c r="B50" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6175,21 +6197,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6199,10 +6221,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581399</v>
+        <v>581511</v>
       </c>
       <c r="R50" t="n">
-        <v>7056764</v>
+        <v>7056763</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6234,7 +6256,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6244,7 +6266,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6259,19 +6286,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120415304</v>
+        <v>120418034</v>
       </c>
       <c r="B51" t="n">
         <v>78278</v>
@@ -6311,10 +6338,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581476</v>
+        <v>581578</v>
       </c>
       <c r="R51" t="n">
-        <v>7056796</v>
+        <v>7056727</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6346,7 +6373,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6356,7 +6383,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6383,7 +6410,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120413734</v>
+        <v>120416085</v>
       </c>
       <c r="B52" t="n">
         <v>57320</v>
@@ -6417,21 +6444,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581614</v>
+        <v>581400</v>
       </c>
       <c r="R52" t="n">
-        <v>7056765</v>
+        <v>7056768</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6463,7 +6485,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6473,7 +6495,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6500,10 +6527,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120415839</v>
+        <v>120413757</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6512,25 +6539,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6540,10 +6567,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581411</v>
+        <v>581599</v>
       </c>
       <c r="R53" t="n">
-        <v>7056774</v>
+        <v>7056800</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6575,7 +6602,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6585,12 +6612,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6617,10 +6639,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120414134</v>
+        <v>120413604</v>
       </c>
       <c r="B54" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6629,42 +6651,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581571</v>
+        <v>581637</v>
       </c>
       <c r="R54" t="n">
-        <v>7056908</v>
+        <v>7056775</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6696,7 +6714,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6706,7 +6724,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6721,22 +6739,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120417594</v>
+        <v>120415835</v>
       </c>
       <c r="B55" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6745,42 +6763,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581404</v>
+        <v>581425</v>
       </c>
       <c r="R55" t="n">
-        <v>7056792</v>
+        <v>7056761</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6812,7 +6826,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6822,7 +6836,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6849,10 +6863,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120416085</v>
+        <v>120414540</v>
       </c>
       <c r="B56" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6861,25 +6875,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6889,10 +6903,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581400</v>
+        <v>581464</v>
       </c>
       <c r="R56" t="n">
-        <v>7056768</v>
+        <v>7056839</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6924,7 +6938,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6934,12 +6948,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6954,19 +6963,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120417801</v>
+        <v>120414432</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -7006,10 +7015,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581511</v>
+        <v>581476</v>
       </c>
       <c r="R57" t="n">
-        <v>7056763</v>
+        <v>7056858</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7041,7 +7050,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7051,12 +7060,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7071,22 +7080,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120417731</v>
+        <v>120413912</v>
       </c>
       <c r="B58" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7095,47 +7104,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581441</v>
+        <v>581608</v>
       </c>
       <c r="R58" t="n">
-        <v>7056809</v>
+        <v>7056867</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 44491-2024 artfynd.xlsx
+++ b/artfynd/A 44491-2024 artfynd.xlsx
@@ -3309,10 +3309,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120418063</v>
+        <v>120414554</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581559</v>
+        <v>581467</v>
       </c>
       <c r="R25" t="n">
-        <v>7056729</v>
+        <v>7056835</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3394,7 +3394,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3409,22 +3414,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120414554</v>
+        <v>120418063</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3437,21 +3442,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3461,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581467</v>
+        <v>581559</v>
       </c>
       <c r="R26" t="n">
-        <v>7056835</v>
+        <v>7056729</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3496,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3506,12 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,12 +3526,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120414867</v>
+        <v>120417462</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4120,25 +4120,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581463</v>
+        <v>581378</v>
       </c>
       <c r="R32" t="n">
-        <v>7056818</v>
+        <v>7056810</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4208,22 +4208,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120417462</v>
+        <v>120413734</v>
       </c>
       <c r="B33" t="n">
-        <v>95225</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4232,38 +4232,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581378</v>
+        <v>581614</v>
       </c>
       <c r="R33" t="n">
-        <v>7056810</v>
+        <v>7056765</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4295,7 +4300,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4305,7 +4310,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4320,22 +4325,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120413734</v>
+        <v>120414867</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4348,39 +4353,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581614</v>
+        <v>581463</v>
       </c>
       <c r="R34" t="n">
-        <v>7056765</v>
+        <v>7056818</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -6298,10 +6298,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120418034</v>
+        <v>120413757</v>
       </c>
       <c r="B51" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6310,25 +6310,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581578</v>
+        <v>581599</v>
       </c>
       <c r="R51" t="n">
-        <v>7056727</v>
+        <v>7056800</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6398,22 +6398,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120416085</v>
+        <v>120418034</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6426,21 +6426,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581400</v>
+        <v>581578</v>
       </c>
       <c r="R52" t="n">
-        <v>7056768</v>
+        <v>7056727</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6495,12 +6495,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6527,10 +6522,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120413757</v>
+        <v>120416085</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6539,25 +6534,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6567,10 +6562,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581599</v>
+        <v>581400</v>
       </c>
       <c r="R53" t="n">
-        <v>7056800</v>
+        <v>7056768</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6602,7 +6597,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6612,7 +6607,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6627,12 +6627,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6751,10 +6751,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120415835</v>
+        <v>120414540</v>
       </c>
       <c r="B55" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6763,25 +6763,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6791,10 +6791,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581425</v>
+        <v>581464</v>
       </c>
       <c r="R55" t="n">
-        <v>7056761</v>
+        <v>7056839</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6851,22 +6851,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120414540</v>
+        <v>120415835</v>
       </c>
       <c r="B56" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6875,25 +6875,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581464</v>
+        <v>581425</v>
       </c>
       <c r="R56" t="n">
-        <v>7056839</v>
+        <v>7056761</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6963,12 +6963,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 44491-2024 artfynd.xlsx
+++ b/artfynd/A 44491-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120417527</v>
+        <v>120417462</v>
       </c>
       <c r="B2" t="n">
-        <v>82321</v>
+        <v>95225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581404</v>
+        <v>581378</v>
       </c>
       <c r="R2" t="n">
-        <v>7056801</v>
+        <v>7056810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120414428</v>
+        <v>120415685</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581533</v>
+        <v>581446</v>
       </c>
       <c r="R3" t="n">
-        <v>7056856</v>
+        <v>7056767</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120413871</v>
+        <v>120413054</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581557</v>
+        <v>581595</v>
       </c>
       <c r="R4" t="n">
-        <v>7056865</v>
+        <v>7056742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120417640</v>
+        <v>120413663</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581428</v>
+        <v>581594</v>
       </c>
       <c r="R5" t="n">
-        <v>7056812</v>
+        <v>7056775</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120417594</v>
+        <v>120417527</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,32 +1145,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
@@ -1175,7 +1176,7 @@
         <v>581404</v>
       </c>
       <c r="R6" t="n">
-        <v>7056792</v>
+        <v>7056801</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120413982</v>
+        <v>120414554</v>
       </c>
       <c r="B7" t="n">
-        <v>95225</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,38 +1257,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581605</v>
+        <v>581467</v>
       </c>
       <c r="R7" t="n">
-        <v>7056913</v>
+        <v>7056835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1330,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120417963</v>
+        <v>120414233</v>
       </c>
       <c r="B8" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581536</v>
+        <v>581514</v>
       </c>
       <c r="R8" t="n">
-        <v>7056710</v>
+        <v>7056850</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120414673</v>
+        <v>120415839</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,42 +1491,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581456</v>
+        <v>581411</v>
       </c>
       <c r="R9" t="n">
-        <v>7056835</v>
+        <v>7056774</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1564,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,19 +1584,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120413560</v>
+        <v>120414155</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1620,14 +1632,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581627</v>
+        <v>581536</v>
       </c>
       <c r="R10" t="n">
-        <v>7056772</v>
+        <v>7056900</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,22 +1696,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120417611</v>
+        <v>120418063</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1736,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581420</v>
+        <v>581559</v>
       </c>
       <c r="R11" t="n">
-        <v>7056797</v>
+        <v>7056729</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,22 +1808,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120413378</v>
+        <v>120414867</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,42 +1832,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581626</v>
+        <v>581463</v>
       </c>
       <c r="R12" t="n">
-        <v>7056697</v>
+        <v>7056818</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120415964</v>
+        <v>120414540</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,47 +1944,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581429</v>
+        <v>581464</v>
       </c>
       <c r="R13" t="n">
-        <v>7056767</v>
+        <v>7056839</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120417911</v>
+        <v>120413441</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,25 +2056,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2085,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581484</v>
+        <v>581631</v>
       </c>
       <c r="R14" t="n">
-        <v>7056713</v>
+        <v>7056710</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120415832</v>
+        <v>120413812</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,39 +2172,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581418</v>
+        <v>581544</v>
       </c>
       <c r="R15" t="n">
-        <v>7056773</v>
+        <v>7056816</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120414445</v>
+        <v>120414428</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,39 +2284,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581491</v>
+        <v>581533</v>
       </c>
       <c r="R16" t="n">
-        <v>7056878</v>
+        <v>7056856</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2364,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120414155</v>
+        <v>120414296</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,34 +2396,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581536</v>
+        <v>581515</v>
       </c>
       <c r="R17" t="n">
-        <v>7056900</v>
+        <v>7056856</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2476,7 +2465,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,22 +2485,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120415304</v>
+        <v>120414432</v>
       </c>
       <c r="B18" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2519,21 +2513,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,7 +2540,7 @@
         <v>581476</v>
       </c>
       <c r="R18" t="n">
-        <v>7056796</v>
+        <v>7056858</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2588,7 +2582,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,19 +2602,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120413054</v>
+        <v>120417801</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2655,10 +2654,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581595</v>
+        <v>581511</v>
       </c>
       <c r="R19" t="n">
-        <v>7056742</v>
+        <v>7056763</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,7 +2689,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,12 +2699,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,22 +2719,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120417685</v>
+        <v>120417731</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,38 +2743,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581428</v>
+        <v>581441</v>
       </c>
       <c r="R20" t="n">
-        <v>7056812</v>
+        <v>7056809</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2807,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2817,7 +2825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,22 +2840,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120417731</v>
+        <v>120417941</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2856,47 +2864,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581441</v>
+        <v>581521</v>
       </c>
       <c r="R21" t="n">
-        <v>7056809</v>
+        <v>7056713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2928,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2938,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3081,7 +3080,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120417497</v>
+        <v>120413604</v>
       </c>
       <c r="B23" t="n">
         <v>79623</v>
@@ -3121,10 +3120,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581473</v>
+        <v>581637</v>
       </c>
       <c r="R23" t="n">
-        <v>7056827</v>
+        <v>7056775</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3156,7 +3155,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3166,7 +3165,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3181,22 +3180,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120413881</v>
+        <v>120413757</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3205,42 +3204,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581588</v>
+        <v>581599</v>
       </c>
       <c r="R24" t="n">
-        <v>7056845</v>
+        <v>7056800</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3272,7 +3267,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3282,7 +3277,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3297,22 +3292,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120414554</v>
+        <v>120413690</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3321,20 +3316,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3342,17 +3337,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581467</v>
+        <v>581626</v>
       </c>
       <c r="R25" t="n">
-        <v>7056835</v>
+        <v>7056776</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3384,7 +3388,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3394,12 +3398,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3414,22 +3413,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120418063</v>
+        <v>120413982</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3438,38 +3437,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581559</v>
+        <v>581605</v>
       </c>
       <c r="R26" t="n">
-        <v>7056729</v>
+        <v>7056913</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,7 +3500,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3510,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,19 +3525,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120413128</v>
+        <v>120416014</v>
       </c>
       <c r="B27" t="n">
         <v>79623</v>
@@ -3578,10 +3577,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581627</v>
+        <v>581399</v>
       </c>
       <c r="R27" t="n">
-        <v>7056700</v>
+        <v>7056764</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3613,7 +3612,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3623,7 +3622,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3650,10 +3649,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120417941</v>
+        <v>120413128</v>
       </c>
       <c r="B28" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3666,21 +3665,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3690,10 +3689,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581521</v>
+        <v>581627</v>
       </c>
       <c r="R28" t="n">
-        <v>7056713</v>
+        <v>7056700</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3725,7 +3724,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3735,7 +3734,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3750,22 +3749,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120414233</v>
+        <v>120417963</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3778,21 +3777,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3802,10 +3801,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581514</v>
+        <v>581536</v>
       </c>
       <c r="R29" t="n">
-        <v>7056850</v>
+        <v>7056710</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3837,7 +3836,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3847,12 +3846,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3879,10 +3873,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120415839</v>
+        <v>120415304</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3895,21 +3889,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3919,10 +3913,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581411</v>
+        <v>581476</v>
       </c>
       <c r="R30" t="n">
-        <v>7056774</v>
+        <v>7056796</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3954,7 +3948,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3964,12 +3958,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,19 +3973,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120415813</v>
+        <v>120417497</v>
       </c>
       <c r="B31" t="n">
         <v>79623</v>
@@ -4036,10 +4025,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581427</v>
+        <v>581473</v>
       </c>
       <c r="R31" t="n">
-        <v>7056778</v>
+        <v>7056827</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4071,7 +4060,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4081,7 +4070,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4096,22 +4085,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120417462</v>
+        <v>120415832</v>
       </c>
       <c r="B32" t="n">
-        <v>95225</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4120,38 +4109,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581378</v>
+        <v>581418</v>
       </c>
       <c r="R32" t="n">
-        <v>7056810</v>
+        <v>7056773</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4183,7 +4177,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4193,7 +4187,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4337,10 +4331,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120414867</v>
+        <v>120414673</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4349,38 +4343,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581463</v>
+        <v>581456</v>
       </c>
       <c r="R34" t="n">
-        <v>7056818</v>
+        <v>7056835</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4412,7 +4410,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4422,7 +4420,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4449,10 +4447,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120416014</v>
+        <v>120417594</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4461,38 +4459,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581399</v>
+        <v>581404</v>
       </c>
       <c r="R35" t="n">
-        <v>7056764</v>
+        <v>7056792</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4524,7 +4526,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4534,7 +4536,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4549,12 +4551,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4673,10 +4675,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120413690</v>
+        <v>120413439</v>
       </c>
       <c r="B37" t="n">
-        <v>57431</v>
+        <v>90545</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4689,43 +4691,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581626</v>
+        <v>581650</v>
       </c>
       <c r="R37" t="n">
-        <v>7056776</v>
+        <v>7056730</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4757,7 +4750,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4767,7 +4760,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4782,22 +4775,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120414296</v>
+        <v>120414134</v>
       </c>
       <c r="B38" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4806,38 +4799,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581515</v>
+        <v>581571</v>
       </c>
       <c r="R38" t="n">
-        <v>7056856</v>
+        <v>7056908</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4869,7 +4866,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4879,12 +4876,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4899,22 +4891,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413812</v>
+        <v>120413881</v>
       </c>
       <c r="B39" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4923,38 +4915,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581544</v>
+        <v>581588</v>
       </c>
       <c r="R39" t="n">
-        <v>7056816</v>
+        <v>7056845</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4986,7 +4982,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4996,7 +4992,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5011,19 +5007,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120415820</v>
+        <v>120415835</v>
       </c>
       <c r="B40" t="n">
         <v>79623</v>
@@ -5063,10 +5059,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581434</v>
+        <v>581425</v>
       </c>
       <c r="R40" t="n">
-        <v>7056778</v>
+        <v>7056761</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5098,7 +5094,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5108,7 +5104,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5123,22 +5119,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120415685</v>
+        <v>120415813</v>
       </c>
       <c r="B41" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5151,39 +5147,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581446</v>
+        <v>581427</v>
       </c>
       <c r="R41" t="n">
-        <v>7056767</v>
+        <v>7056778</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5215,7 +5206,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5225,7 +5216,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5240,22 +5231,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120415894</v>
+        <v>120417640</v>
       </c>
       <c r="B42" t="n">
-        <v>5169</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5264,43 +5255,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581399</v>
+        <v>581428</v>
       </c>
       <c r="R42" t="n">
-        <v>7056765</v>
+        <v>7056812</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5332,7 +5318,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5342,7 +5328,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5357,22 +5348,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120417814</v>
+        <v>120418034</v>
       </c>
       <c r="B43" t="n">
-        <v>56535</v>
+        <v>78278</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5381,51 +5372,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581488</v>
+        <v>581578</v>
       </c>
       <c r="R43" t="n">
-        <v>7056733</v>
+        <v>7056727</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5454,7 +5435,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5464,7 +5445,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5479,22 +5460,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120413439</v>
+        <v>120415855</v>
       </c>
       <c r="B44" t="n">
-        <v>90545</v>
+        <v>57473</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5503,38 +5484,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581650</v>
+        <v>581426</v>
       </c>
       <c r="R44" t="n">
-        <v>7056730</v>
+        <v>7056764</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5566,7 +5556,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5576,7 +5566,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5591,22 +5581,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120415855</v>
+        <v>120413378</v>
       </c>
       <c r="B45" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5615,35 +5605,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5652,10 +5637,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581426</v>
+        <v>581626</v>
       </c>
       <c r="R45" t="n">
-        <v>7056764</v>
+        <v>7056697</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5687,7 +5672,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5697,7 +5682,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5724,7 +5709,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120414134</v>
+        <v>120415964</v>
       </c>
       <c r="B46" t="n">
         <v>97930</v>
@@ -5759,19 +5744,24 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581571</v>
+        <v>581429</v>
       </c>
       <c r="R46" t="n">
-        <v>7056908</v>
+        <v>7056767</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5803,7 +5793,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5813,7 +5803,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5828,19 +5818,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120413663</v>
+        <v>120417685</v>
       </c>
       <c r="B47" t="n">
         <v>79623</v>
@@ -5880,10 +5870,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581594</v>
+        <v>581428</v>
       </c>
       <c r="R47" t="n">
-        <v>7056775</v>
+        <v>7056812</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5915,7 +5905,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5925,7 +5915,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5952,10 +5942,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120415732</v>
+        <v>120414445</v>
       </c>
       <c r="B48" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5968,34 +5958,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581439</v>
+        <v>581491</v>
       </c>
       <c r="R48" t="n">
-        <v>7056768</v>
+        <v>7056878</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6027,7 +6022,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6037,12 +6032,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6057,22 +6047,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120413441</v>
+        <v>120413912</v>
       </c>
       <c r="B49" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6085,21 +6075,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6109,10 +6099,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581631</v>
+        <v>581608</v>
       </c>
       <c r="R49" t="n">
-        <v>7056710</v>
+        <v>7056867</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6144,7 +6134,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6154,7 +6144,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6181,10 +6171,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120417801</v>
+        <v>120415894</v>
       </c>
       <c r="B50" t="n">
-        <v>57320</v>
+        <v>5169</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6193,38 +6183,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581511</v>
+        <v>581399</v>
       </c>
       <c r="R50" t="n">
-        <v>7056763</v>
+        <v>7056765</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6256,7 +6251,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6266,12 +6261,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6298,10 +6288,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120413757</v>
+        <v>120413560</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6310,25 +6300,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6338,10 +6328,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581599</v>
+        <v>581627</v>
       </c>
       <c r="R51" t="n">
-        <v>7056800</v>
+        <v>7056772</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6373,7 +6363,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6383,7 +6373,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6410,10 +6400,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120418034</v>
+        <v>120417814</v>
       </c>
       <c r="B52" t="n">
-        <v>78278</v>
+        <v>56535</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6422,41 +6412,51 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581578</v>
+        <v>581488</v>
       </c>
       <c r="R52" t="n">
-        <v>7056727</v>
+        <v>7056733</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6510,22 +6510,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120416085</v>
+        <v>120417611</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6538,21 +6538,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6562,10 +6562,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581400</v>
+        <v>581420</v>
       </c>
       <c r="R53" t="n">
-        <v>7056768</v>
+        <v>7056797</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6607,12 +6607,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6627,19 +6622,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120413604</v>
+        <v>120415732</v>
       </c>
       <c r="B54" t="n">
         <v>79623</v>
@@ -6679,10 +6674,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581637</v>
+        <v>581439</v>
       </c>
       <c r="R54" t="n">
-        <v>7056775</v>
+        <v>7056768</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6714,7 +6709,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6724,7 +6719,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Lunglav på asp</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6751,10 +6751,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120414540</v>
+        <v>120416085</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6763,25 +6763,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6791,10 +6791,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581464</v>
+        <v>581400</v>
       </c>
       <c r="R55" t="n">
-        <v>7056839</v>
+        <v>7056768</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6836,7 +6836,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6851,22 +6856,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120415835</v>
+        <v>120417911</v>
       </c>
       <c r="B56" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6875,25 +6880,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6903,10 +6908,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581425</v>
+        <v>581484</v>
       </c>
       <c r="R56" t="n">
-        <v>7056761</v>
+        <v>7056713</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6938,7 +6943,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6948,7 +6953,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6975,10 +6980,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120414432</v>
+        <v>120415820</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6991,21 +6996,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7015,10 +7020,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581476</v>
+        <v>581434</v>
       </c>
       <c r="R57" t="n">
-        <v>7056858</v>
+        <v>7056778</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7050,7 +7055,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7060,12 +7065,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7092,10 +7092,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120413912</v>
+        <v>120413871</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7108,21 +7108,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581608</v>
+        <v>581557</v>
       </c>
       <c r="R58" t="n">
-        <v>7056867</v>
+        <v>7056865</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7192,12 +7192,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 44491-2024 artfynd.xlsx
+++ b/artfynd/A 44491-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120417462</v>
+        <v>120414540</v>
       </c>
       <c r="B2" t="n">
-        <v>95225</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581378</v>
+        <v>581464</v>
       </c>
       <c r="R2" t="n">
-        <v>7056810</v>
+        <v>7056839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120415685</v>
+        <v>120415820</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581446</v>
+        <v>581434</v>
       </c>
       <c r="R3" t="n">
-        <v>7056767</v>
+        <v>7056778</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120413054</v>
+        <v>120413378</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +911,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581595</v>
+        <v>581626</v>
       </c>
       <c r="R4" t="n">
-        <v>7056742</v>
+        <v>7056697</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120413663</v>
+        <v>120414673</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1027,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581594</v>
+        <v>581456</v>
       </c>
       <c r="R5" t="n">
-        <v>7056775</v>
+        <v>7056835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1119,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120417527</v>
+        <v>120415839</v>
       </c>
       <c r="B6" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581404</v>
+        <v>581411</v>
       </c>
       <c r="R6" t="n">
-        <v>7056801</v>
+        <v>7056774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1216,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,19 +1236,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120414554</v>
+        <v>120416085</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1285,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581467</v>
+        <v>581400</v>
       </c>
       <c r="R7" t="n">
-        <v>7056835</v>
+        <v>7056768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1333,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,19 +1353,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120414233</v>
+        <v>120417801</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1402,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581514</v>
+        <v>581511</v>
       </c>
       <c r="R8" t="n">
-        <v>7056850</v>
+        <v>7056763</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1450,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1470,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120415839</v>
+        <v>120417594</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,38 +1494,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581411</v>
+        <v>581404</v>
       </c>
       <c r="R9" t="n">
-        <v>7056774</v>
+        <v>7056792</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,12 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1586,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120414155</v>
+        <v>120416014</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,34 +1614,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581536</v>
+        <v>581399</v>
       </c>
       <c r="R10" t="n">
-        <v>7056900</v>
+        <v>7056764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,22 +1698,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120418063</v>
+        <v>120413441</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1750,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581559</v>
+        <v>581631</v>
       </c>
       <c r="R11" t="n">
-        <v>7056729</v>
+        <v>7056710</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120414867</v>
+        <v>120417497</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581463</v>
+        <v>581473</v>
       </c>
       <c r="R12" t="n">
-        <v>7056818</v>
+        <v>7056827</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120414540</v>
+        <v>120414867</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,25 +1946,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581464</v>
+        <v>581463</v>
       </c>
       <c r="R13" t="n">
-        <v>7056839</v>
+        <v>7056818</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,22 +2034,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120413441</v>
+        <v>120413560</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,21 +2062,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581631</v>
+        <v>581627</v>
       </c>
       <c r="R14" t="n">
-        <v>7056710</v>
+        <v>7056772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,22 +2146,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120413812</v>
+        <v>120414554</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,21 +2174,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2198,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581544</v>
+        <v>581467</v>
       </c>
       <c r="R15" t="n">
-        <v>7056816</v>
+        <v>7056835</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2243,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2275,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120414428</v>
+        <v>120413734</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,34 +2291,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581533</v>
+        <v>581614</v>
       </c>
       <c r="R16" t="n">
-        <v>7056856</v>
+        <v>7056765</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120414296</v>
+        <v>120415813</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,21 +2408,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581515</v>
+        <v>581427</v>
       </c>
       <c r="R17" t="n">
-        <v>7056856</v>
+        <v>7056778</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2455,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,12 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120414432</v>
+        <v>120413812</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,21 +2520,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2537,10 +2544,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581476</v>
+        <v>581544</v>
       </c>
       <c r="R18" t="n">
-        <v>7056858</v>
+        <v>7056816</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2572,7 +2579,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,12 +2589,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,10 +2616,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120417801</v>
+        <v>120414155</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,34 +2632,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581511</v>
+        <v>581536</v>
       </c>
       <c r="R19" t="n">
-        <v>7056763</v>
+        <v>7056900</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2689,7 +2691,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2699,12 +2701,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,10 +2728,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120417731</v>
+        <v>120417640</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2743,47 +2740,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581441</v>
+        <v>581428</v>
       </c>
       <c r="R20" t="n">
-        <v>7056809</v>
+        <v>7056812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2803,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2813,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2840,22 +2833,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120417941</v>
+        <v>120414233</v>
       </c>
       <c r="B21" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,21 +2861,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2892,10 +2885,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581521</v>
+        <v>581514</v>
       </c>
       <c r="R21" t="n">
-        <v>7056713</v>
+        <v>7056850</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,7 +2920,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2930,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2952,22 +2950,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120413917</v>
+        <v>120417527</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2976,42 +2974,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581610</v>
+        <v>581404</v>
       </c>
       <c r="R22" t="n">
-        <v>7056879</v>
+        <v>7056801</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3043,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3053,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120413604</v>
+        <v>120417963</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>78279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3096,21 +3090,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3120,10 +3114,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581637</v>
+        <v>581536</v>
       </c>
       <c r="R23" t="n">
-        <v>7056775</v>
+        <v>7056710</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3155,7 +3149,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3165,7 +3159,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120413757</v>
+        <v>120413912</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,25 +3198,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581599</v>
+        <v>581608</v>
       </c>
       <c r="R24" t="n">
-        <v>7056800</v>
+        <v>7056867</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3267,7 +3261,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3271,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3292,22 +3286,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120413690</v>
+        <v>120415304</v>
       </c>
       <c r="B25" t="n">
-        <v>57431</v>
+        <v>78278</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3316,47 +3310,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581626</v>
+        <v>581476</v>
       </c>
       <c r="R25" t="n">
-        <v>7056776</v>
+        <v>7056796</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3388,7 +3373,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3398,7 +3383,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3425,10 +3410,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120413982</v>
+        <v>120415964</v>
       </c>
       <c r="B26" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3437,38 +3422,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581605</v>
+        <v>581429</v>
       </c>
       <c r="R26" t="n">
-        <v>7056913</v>
+        <v>7056767</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3500,7 +3494,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3510,7 +3504,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3537,10 +3531,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120416014</v>
+        <v>120418034</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3553,21 +3547,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3577,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581399</v>
+        <v>581578</v>
       </c>
       <c r="R27" t="n">
-        <v>7056764</v>
+        <v>7056727</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3612,7 +3606,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3622,7 +3616,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3637,19 +3631,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120413128</v>
+        <v>120413604</v>
       </c>
       <c r="B28" t="n">
         <v>79623</v>
@@ -3689,10 +3683,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581627</v>
+        <v>581637</v>
       </c>
       <c r="R28" t="n">
-        <v>7056700</v>
+        <v>7056775</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3724,7 +3718,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3734,7 +3728,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3761,10 +3755,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120417963</v>
+        <v>120414296</v>
       </c>
       <c r="B29" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3777,21 +3771,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3801,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581536</v>
+        <v>581515</v>
       </c>
       <c r="R29" t="n">
-        <v>7056710</v>
+        <v>7056856</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3836,7 +3830,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3846,7 +3840,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3873,10 +3872,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120415304</v>
+        <v>120417462</v>
       </c>
       <c r="B30" t="n">
-        <v>78278</v>
+        <v>95225</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3885,25 +3884,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3913,10 +3912,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581476</v>
+        <v>581378</v>
       </c>
       <c r="R30" t="n">
-        <v>7056796</v>
+        <v>7056810</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3948,7 +3947,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3958,7 +3957,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3973,19 +3972,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120417497</v>
+        <v>120413871</v>
       </c>
       <c r="B31" t="n">
         <v>79623</v>
@@ -4025,10 +4024,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581473</v>
+        <v>581557</v>
       </c>
       <c r="R31" t="n">
-        <v>7056827</v>
+        <v>7056865</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,7 +4059,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4070,7 +4069,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4085,22 +4084,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120415832</v>
+        <v>120415855</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4113,27 +4112,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4142,10 +4145,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581418</v>
+        <v>581426</v>
       </c>
       <c r="R32" t="n">
-        <v>7056773</v>
+        <v>7056764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4177,7 +4180,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4187,7 +4190,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4202,22 +4205,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120413734</v>
+        <v>120413917</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4226,31 +4229,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4259,10 +4261,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581614</v>
+        <v>581610</v>
       </c>
       <c r="R33" t="n">
-        <v>7056765</v>
+        <v>7056879</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4294,7 +4296,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4304,7 +4306,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4331,10 +4333,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120414673</v>
+        <v>120414428</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4343,42 +4345,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581456</v>
+        <v>581533</v>
       </c>
       <c r="R34" t="n">
-        <v>7056835</v>
+        <v>7056856</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4410,7 +4408,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4420,7 +4418,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4447,10 +4445,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120417594</v>
+        <v>120414445</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4459,30 +4457,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4491,10 +4490,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581404</v>
+        <v>581491</v>
       </c>
       <c r="R35" t="n">
-        <v>7056792</v>
+        <v>7056878</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4526,7 +4525,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4536,7 +4535,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4563,10 +4562,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120417662</v>
+        <v>120413757</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4575,25 +4574,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4603,10 +4602,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581434</v>
+        <v>581599</v>
       </c>
       <c r="R36" t="n">
-        <v>7056811</v>
+        <v>7056800</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4638,7 +4637,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4647,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4663,22 +4662,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120413439</v>
+        <v>120417685</v>
       </c>
       <c r="B37" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4687,25 +4686,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4715,10 +4714,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581650</v>
+        <v>581428</v>
       </c>
       <c r="R37" t="n">
-        <v>7056730</v>
+        <v>7056812</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4750,7 +4749,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4760,7 +4759,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4787,10 +4786,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120414134</v>
+        <v>120415685</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4799,42 +4798,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581571</v>
+        <v>581446</v>
       </c>
       <c r="R38" t="n">
-        <v>7056908</v>
+        <v>7056767</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4903,7 +4903,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120413881</v>
+        <v>120417731</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -4938,7 +4938,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4947,10 +4952,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581588</v>
+        <v>581441</v>
       </c>
       <c r="R39" t="n">
-        <v>7056845</v>
+        <v>7056809</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4982,7 +4987,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4992,7 +4997,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5019,10 +5024,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120415835</v>
+        <v>120413982</v>
       </c>
       <c r="B40" t="n">
-        <v>79623</v>
+        <v>95225</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5031,38 +5036,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581425</v>
+        <v>581605</v>
       </c>
       <c r="R40" t="n">
-        <v>7056761</v>
+        <v>7056913</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5094,7 +5099,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5104,7 +5109,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5119,19 +5124,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120415813</v>
+        <v>120415732</v>
       </c>
       <c r="B41" t="n">
         <v>79623</v>
@@ -5171,10 +5176,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581427</v>
+        <v>581439</v>
       </c>
       <c r="R41" t="n">
-        <v>7056778</v>
+        <v>7056768</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5206,7 +5211,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5216,7 +5221,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Lunglav på asp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,10 +5253,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120417640</v>
+        <v>120413128</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5259,21 +5269,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5283,10 +5293,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581428</v>
+        <v>581627</v>
       </c>
       <c r="R42" t="n">
-        <v>7056812</v>
+        <v>7056700</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5318,7 +5328,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5328,12 +5338,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5360,10 +5365,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120418034</v>
+        <v>120415832</v>
       </c>
       <c r="B43" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5376,34 +5381,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581578</v>
+        <v>581418</v>
       </c>
       <c r="R43" t="n">
-        <v>7056727</v>
+        <v>7056773</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5435,7 +5445,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5445,7 +5455,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5460,22 +5470,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120415855</v>
+        <v>120414432</v>
       </c>
       <c r="B44" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5488,43 +5498,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581426</v>
+        <v>581476</v>
       </c>
       <c r="R44" t="n">
-        <v>7056764</v>
+        <v>7056858</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5556,7 +5557,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5566,7 +5567,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5581,22 +5587,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120413378</v>
+        <v>120413054</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5605,42 +5611,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581626</v>
+        <v>581595</v>
       </c>
       <c r="R45" t="n">
-        <v>7056697</v>
+        <v>7056742</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5672,7 +5674,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5682,7 +5684,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5697,22 +5704,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120415964</v>
+        <v>120415894</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>5169</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5721,35 +5728,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5758,10 +5761,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581429</v>
+        <v>581399</v>
       </c>
       <c r="R46" t="n">
-        <v>7056767</v>
+        <v>7056765</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5793,7 +5796,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5803,7 +5806,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5818,19 +5821,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120417685</v>
+        <v>120413663</v>
       </c>
       <c r="B47" t="n">
         <v>79623</v>
@@ -5870,10 +5873,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581428</v>
+        <v>581594</v>
       </c>
       <c r="R47" t="n">
-        <v>7056812</v>
+        <v>7056775</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5905,7 +5908,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5915,7 +5918,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5942,10 +5945,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120414445</v>
+        <v>120417941</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5958,39 +5961,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581491</v>
+        <v>581521</v>
       </c>
       <c r="R48" t="n">
-        <v>7056878</v>
+        <v>7056713</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6022,7 +6020,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6032,7 +6030,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6059,10 +6057,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120413912</v>
+        <v>120415835</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6075,21 +6073,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6099,10 +6097,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581608</v>
+        <v>581425</v>
       </c>
       <c r="R49" t="n">
-        <v>7056867</v>
+        <v>7056761</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6134,7 +6132,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6144,7 +6142,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6171,10 +6169,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120415894</v>
+        <v>120417611</v>
       </c>
       <c r="B50" t="n">
-        <v>5169</v>
+        <v>90580</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6183,43 +6181,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581399</v>
+        <v>581420</v>
       </c>
       <c r="R50" t="n">
-        <v>7056765</v>
+        <v>7056797</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6251,7 +6244,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6261,7 +6254,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6276,22 +6269,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120413560</v>
+        <v>120414134</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6300,38 +6293,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581627</v>
+        <v>581571</v>
       </c>
       <c r="R51" t="n">
-        <v>7056772</v>
+        <v>7056908</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6363,7 +6360,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6373,7 +6370,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6388,22 +6385,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120417814</v>
+        <v>120413690</v>
       </c>
       <c r="B52" t="n">
-        <v>56535</v>
+        <v>57431</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6416,16 +6413,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6433,15 +6430,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6450,13 +6446,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581488</v>
+        <v>581626</v>
       </c>
       <c r="R52" t="n">
-        <v>7056733</v>
+        <v>7056776</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6485,7 +6481,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6495,7 +6491,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6510,22 +6506,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120417611</v>
+        <v>120418063</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6538,21 +6534,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6562,10 +6558,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581420</v>
+        <v>581559</v>
       </c>
       <c r="R53" t="n">
-        <v>7056797</v>
+        <v>7056729</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6597,7 +6593,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6607,7 +6603,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6622,22 +6618,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120415732</v>
+        <v>120413439</v>
       </c>
       <c r="B54" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6646,25 +6642,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6674,10 +6670,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581439</v>
+        <v>581650</v>
       </c>
       <c r="R54" t="n">
-        <v>7056768</v>
+        <v>7056730</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6709,7 +6705,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6719,12 +6715,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6751,10 +6742,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120416085</v>
+        <v>120417814</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>56535</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6763,20 +6754,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6785,19 +6776,29 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581400</v>
+        <v>581488</v>
       </c>
       <c r="R55" t="n">
-        <v>7056768</v>
+        <v>7056733</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6826,7 +6827,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6836,12 +6837,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6856,22 +6852,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120417911</v>
+        <v>120417662</v>
       </c>
       <c r="B56" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6880,25 +6876,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6908,10 +6904,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581484</v>
+        <v>581434</v>
       </c>
       <c r="R56" t="n">
-        <v>7056713</v>
+        <v>7056811</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6943,7 +6939,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6953,7 +6949,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6980,10 +6976,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120415820</v>
+        <v>120413881</v>
       </c>
       <c r="B57" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6992,38 +6988,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581434</v>
+        <v>581588</v>
       </c>
       <c r="R57" t="n">
-        <v>7056778</v>
+        <v>7056845</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7080,22 +7080,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120413871</v>
+        <v>120417911</v>
       </c>
       <c r="B58" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7104,25 +7104,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581557</v>
+        <v>581484</v>
       </c>
       <c r="R58" t="n">
-        <v>7056865</v>
+        <v>7056713</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7192,12 +7192,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 44491-2024 artfynd.xlsx
+++ b/artfynd/A 44491-2024 artfynd.xlsx
@@ -3872,10 +3872,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120417462</v>
+        <v>120415855</v>
       </c>
       <c r="B30" t="n">
-        <v>95225</v>
+        <v>57473</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3884,38 +3884,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581378</v>
+        <v>581426</v>
       </c>
       <c r="R30" t="n">
-        <v>7056810</v>
+        <v>7056764</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,7 +3956,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3957,7 +3966,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3972,22 +3981,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120413871</v>
+        <v>120413917</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3996,38 +4005,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581557</v>
+        <v>581610</v>
       </c>
       <c r="R31" t="n">
-        <v>7056865</v>
+        <v>7056879</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4059,7 +4072,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4069,7 +4082,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4084,22 +4097,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120415855</v>
+        <v>120417462</v>
       </c>
       <c r="B32" t="n">
-        <v>57473</v>
+        <v>95225</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4108,47 +4121,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581426</v>
+        <v>581378</v>
       </c>
       <c r="R32" t="n">
-        <v>7056764</v>
+        <v>7056810</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4180,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4190,7 +4194,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4205,22 +4209,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120413917</v>
+        <v>120413871</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4229,42 +4233,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581610</v>
+        <v>581557</v>
       </c>
       <c r="R33" t="n">
-        <v>7056879</v>
+        <v>7056865</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4321,12 +4321,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120413757</v>
+        <v>120415685</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4574,38 +4574,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581599</v>
+        <v>581446</v>
       </c>
       <c r="R36" t="n">
-        <v>7056800</v>
+        <v>7056767</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4637,7 +4642,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4647,7 +4652,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4662,22 +4667,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120417685</v>
+        <v>120413757</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4686,25 +4691,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4714,10 +4719,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581428</v>
+        <v>581599</v>
       </c>
       <c r="R37" t="n">
-        <v>7056812</v>
+        <v>7056800</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4749,7 +4754,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4759,7 +4764,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4786,10 +4791,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120415685</v>
+        <v>120417685</v>
       </c>
       <c r="B38" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4802,39 +4807,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581446</v>
+        <v>581428</v>
       </c>
       <c r="R38" t="n">
-        <v>7056767</v>
+        <v>7056812</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4891,12 +4891,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5136,10 +5136,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120415732</v>
+        <v>120415832</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5152,34 +5152,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581439</v>
+        <v>581418</v>
       </c>
       <c r="R41" t="n">
-        <v>7056768</v>
+        <v>7056773</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5211,7 +5216,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5221,12 +5226,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Lunglav på asp</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5253,10 +5253,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120413128</v>
+        <v>120414432</v>
       </c>
       <c r="B42" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5269,21 +5269,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581627</v>
+        <v>581476</v>
       </c>
       <c r="R42" t="n">
-        <v>7056700</v>
+        <v>7056858</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5338,7 +5338,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5365,7 +5370,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120415832</v>
+        <v>120413054</v>
       </c>
       <c r="B43" t="n">
         <v>57320</v>
@@ -5399,21 +5404,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581418</v>
+        <v>581595</v>
       </c>
       <c r="R43" t="n">
-        <v>7056773</v>
+        <v>7056742</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5455,7 +5455,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5482,10 +5487,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120414432</v>
+        <v>120415732</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5498,21 +5503,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5522,10 +5527,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581476</v>
+        <v>581439</v>
       </c>
       <c r="R44" t="n">
-        <v>7056858</v>
+        <v>7056768</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5557,7 +5562,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5567,12 +5572,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lunglav på asp</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5599,10 +5604,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120413054</v>
+        <v>120413128</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5615,21 +5620,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5639,10 +5644,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581595</v>
+        <v>581627</v>
       </c>
       <c r="R45" t="n">
-        <v>7056742</v>
+        <v>7056700</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5674,7 +5679,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5684,12 +5689,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6057,10 +6057,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120415835</v>
+        <v>120414134</v>
       </c>
       <c r="B49" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6069,38 +6069,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
+          <t>Tarån, Tarån, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581425</v>
+        <v>581571</v>
       </c>
       <c r="R49" t="n">
-        <v>7056761</v>
+        <v>7056908</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6132,7 +6136,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6142,7 +6146,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6169,10 +6173,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120417611</v>
+        <v>120415835</v>
       </c>
       <c r="B50" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6185,21 +6189,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6209,10 +6213,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581420</v>
+        <v>581425</v>
       </c>
       <c r="R50" t="n">
-        <v>7056797</v>
+        <v>7056761</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6244,7 +6248,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6254,7 +6258,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6269,22 +6273,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120414134</v>
+        <v>120417611</v>
       </c>
       <c r="B51" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6293,42 +6297,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tarån, Tarån, Ång</t>
+          <t>Bjännkällbäcken, Bjännkällbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581571</v>
+        <v>581420</v>
       </c>
       <c r="R51" t="n">
-        <v>7056908</v>
+        <v>7056797</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6385,12 +6385,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
